--- a/chancado/develop/Report/Lote-Export-Base.xlsx
+++ b/chancado/develop/Report/Lote-Export-Base.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\projects\minersoft-projects\minersoft\acopio-project-configuration\chancado\develop\Report\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\projects\minersoft-projects\minersoft\acopio-chancado-api\Acopio.Chancado.Apis\Report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C2044E4-FD90-47AA-81B1-0FF4682415BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7063DA7D-3858-47C1-8AAE-A1849E96DE23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -418,7 +418,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="22" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -457,22 +457,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="22" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="22" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="22" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="22" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -554,6 +545,12 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="25">
@@ -583,7 +580,7 @@
     <cellStyle name="Normal 2 2 2 2" xfId="24" xr:uid="{7D02EEDF-F966-42E2-BF75-AE97ED01237A}"/>
     <cellStyle name="Normal 3" xfId="23" xr:uid="{00000000-0005-0000-0000-00001C000000}"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="7">
     <dxf>
       <font>
         <b/>
@@ -637,23 +634,6 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <gradientFill type="path" left="0.5" right="0.5" top="0.5" bottom="0.5">
-          <stop position="0">
-            <color theme="0"/>
-          </stop>
-          <stop position="1">
-            <color theme="1"/>
-          </stop>
-        </gradientFill>
-      </fill>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill>
           <bgColor rgb="FFCCFFCC"/>
@@ -675,13 +655,6 @@
             <color theme="1"/>
           </stop>
         </gradientFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFCCFFCC"/>
-        </patternFill>
       </fill>
     </dxf>
   </dxfs>
@@ -753,6 +726,9 @@
       <rgbColor rgb="00333399"/>
       <rgbColor rgb="00333333"/>
     </indexedColors>
+    <mruColors>
+      <color rgb="FFFFFFFF"/>
+    </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -941,39 +917,41 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BF2185"/>
+  <dimension ref="A1:BF12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="6.77734375" style="26" customWidth="1"/>
-    <col min="2" max="2" width="19.77734375" style="27" customWidth="1"/>
-    <col min="3" max="3" width="19.5546875" style="28" customWidth="1"/>
-    <col min="4" max="4" width="19.5546875" style="26" customWidth="1"/>
-    <col min="5" max="5" width="16.6640625" style="26" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.77734375" style="26" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.5546875" style="29" customWidth="1"/>
-    <col min="8" max="8" width="10" style="29" customWidth="1"/>
-    <col min="9" max="9" width="9.109375" style="26" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="44.88671875" style="26" customWidth="1"/>
-    <col min="11" max="11" width="25.77734375" style="26" customWidth="1"/>
-    <col min="12" max="12" width="52.5546875" style="26" customWidth="1"/>
-    <col min="13" max="13" width="19.88671875" style="26" customWidth="1"/>
-    <col min="14" max="14" width="15" style="26" customWidth="1"/>
-    <col min="15" max="15" width="17.33203125" style="26" customWidth="1"/>
-    <col min="16" max="16" width="10.33203125" style="30" customWidth="1"/>
-    <col min="17" max="17" width="12.21875" style="30" customWidth="1"/>
-    <col min="18" max="18" width="10.44140625" style="27" customWidth="1"/>
-    <col min="19" max="19" width="12.5546875" style="27" customWidth="1"/>
-    <col min="20" max="20" width="10.6640625" style="31"/>
-    <col min="21" max="21" width="10.6640625" style="33"/>
-    <col min="22" max="22" width="10.6640625" style="34"/>
-    <col min="23" max="23" width="14.6640625" style="26" customWidth="1"/>
-    <col min="24" max="24" width="13.77734375" style="26" customWidth="1"/>
-    <col min="25" max="28" width="10.6640625" style="26"/>
-    <col min="29" max="29" width="14.109375" style="26" customWidth="1"/>
-    <col min="30" max="30" width="14.109375" style="35" customWidth="1"/>
-    <col min="31" max="31" width="18.5546875" style="26" customWidth="1"/>
-    <col min="32" max="32" width="27.109375" style="26" customWidth="1"/>
-    <col min="33" max="16384" width="10.6640625" style="25"/>
+    <col min="1" max="1" width="6.77734375" style="23" customWidth="1"/>
+    <col min="2" max="2" width="19.77734375" style="24" customWidth="1"/>
+    <col min="3" max="3" width="19.5546875" style="25" customWidth="1"/>
+    <col min="4" max="4" width="19.5546875" style="23" customWidth="1"/>
+    <col min="5" max="5" width="16.6640625" style="23" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.77734375" style="23" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.5546875" style="26" customWidth="1"/>
+    <col min="8" max="8" width="10" style="26" customWidth="1"/>
+    <col min="9" max="9" width="9.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="44.88671875" style="23" customWidth="1"/>
+    <col min="11" max="11" width="25.77734375" style="23" customWidth="1"/>
+    <col min="12" max="12" width="52.5546875" style="23" customWidth="1"/>
+    <col min="13" max="13" width="19.88671875" style="23" customWidth="1"/>
+    <col min="14" max="14" width="15" style="23" customWidth="1"/>
+    <col min="15" max="15" width="17.33203125" style="23" customWidth="1"/>
+    <col min="16" max="16" width="10.33203125" style="27" customWidth="1"/>
+    <col min="17" max="17" width="12.21875" style="27" customWidth="1"/>
+    <col min="18" max="18" width="10.44140625" style="24" customWidth="1"/>
+    <col min="19" max="19" width="12.5546875" style="24" customWidth="1"/>
+    <col min="20" max="20" width="10.6640625" style="28"/>
+    <col min="21" max="21" width="10.6640625" style="30"/>
+    <col min="22" max="22" width="10.6640625" style="31"/>
+    <col min="23" max="23" width="14.6640625" style="23" customWidth="1"/>
+    <col min="24" max="24" width="13.77734375" style="23" customWidth="1"/>
+    <col min="25" max="26" width="10.6640625" style="23"/>
+    <col min="27" max="27" width="22.109375" style="23" customWidth="1"/>
+    <col min="28" max="28" width="24.5546875" style="23" customWidth="1"/>
+    <col min="29" max="29" width="20.5546875" style="23" customWidth="1"/>
+    <col min="30" max="30" width="14.109375" style="32" customWidth="1"/>
+    <col min="31" max="31" width="18.5546875" style="23" customWidth="1"/>
+    <col min="32" max="32" width="27.109375" style="23" customWidth="1"/>
+    <col min="33" max="16384" width="10.6640625" style="22"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:58" customFormat="1" x14ac:dyDescent="0.3">
@@ -987,7 +965,7 @@
       <c r="H1" s="13"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
-      <c r="K1" s="16"/>
+      <c r="K1" s="15"/>
       <c r="L1" s="3"/>
       <c r="M1" s="3"/>
       <c r="N1" s="3"/>
@@ -1037,21 +1015,21 @@
       <c r="BF1" s="3"/>
     </row>
     <row r="2" spans="1:58" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="36" t="s">
+      <c r="A2" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="36"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="36"/>
-      <c r="I2" s="36"/>
-      <c r="J2" s="36"/>
-      <c r="K2" s="36"/>
-      <c r="L2" s="36"/>
-      <c r="M2" s="36"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="33"/>
+      <c r="K2" s="33"/>
+      <c r="L2" s="33"/>
+      <c r="M2" s="33"/>
       <c r="N2" s="2"/>
       <c r="O2" s="4"/>
       <c r="P2" s="3"/>
@@ -1099,21 +1077,21 @@
       <c r="BF2" s="3"/>
     </row>
     <row r="3" spans="1:58" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="37" t="s">
+      <c r="A3" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="37"/>
-      <c r="C3" s="37"/>
-      <c r="D3" s="37"/>
-      <c r="E3" s="37"/>
-      <c r="F3" s="37"/>
-      <c r="G3" s="37"/>
-      <c r="H3" s="37"/>
-      <c r="I3" s="37"/>
-      <c r="J3" s="37"/>
-      <c r="K3" s="37"/>
-      <c r="L3" s="37"/>
-      <c r="M3" s="37"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
+      <c r="J3" s="34"/>
+      <c r="K3" s="34"/>
+      <c r="L3" s="34"/>
+      <c r="M3" s="34"/>
       <c r="N3" s="1"/>
       <c r="O3" s="5"/>
       <c r="P3" s="3"/>
@@ -1160,20 +1138,20 @@
       <c r="BE3" s="3"/>
       <c r="BF3" s="3"/>
     </row>
-    <row r="4" spans="1:58" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="14"/>
-      <c r="H4" s="14"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4"/>
+    <row r="4" spans="1:58" customFormat="1" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="33"/>
+      <c r="B4" s="33"/>
+      <c r="C4" s="33"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="33"/>
+      <c r="G4" s="33"/>
+      <c r="H4" s="33"/>
+      <c r="I4" s="33"/>
+      <c r="J4" s="33"/>
+      <c r="K4" s="33"/>
+      <c r="L4" s="33"/>
+      <c r="M4" s="33"/>
       <c r="N4" s="4"/>
       <c r="O4" s="3"/>
       <c r="P4" s="3"/>
@@ -1227,11 +1205,11 @@
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
-      <c r="G5" s="15"/>
-      <c r="H5" s="15"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="14"/>
       <c r="I5" s="7"/>
       <c r="J5" s="7"/>
-      <c r="K5" s="18"/>
+      <c r="K5" s="16"/>
       <c r="L5" s="7"/>
       <c r="M5" s="7"/>
       <c r="N5" s="8"/>
@@ -1240,7 +1218,7 @@
     <row r="6" spans="1:58" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A6" s="6"/>
       <c r="B6" s="6"/>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="44" t="s">
         <v>2</v>
       </c>
       <c r="D6" s="9"/>
@@ -1250,7 +1228,7 @@
       <c r="H6" s="10"/>
       <c r="I6" s="6"/>
       <c r="J6" s="6"/>
-      <c r="K6" s="19" t="s">
+      <c r="K6" s="43" t="s">
         <v>3</v>
       </c>
       <c r="L6" s="11"/>
@@ -1265,163 +1243,160 @@
       <c r="F7" s="6"/>
       <c r="G7" s="6"/>
       <c r="H7" s="6"/>
-      <c r="I7" s="20"/>
+      <c r="I7" s="17"/>
       <c r="J7" s="6"/>
       <c r="K7" s="6"/>
       <c r="L7" s="6"/>
       <c r="M7" s="6"/>
-      <c r="T7" s="24"/>
+      <c r="T7" s="21"/>
     </row>
-    <row r="8" spans="1:58" s="21" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="38" t="s">
+    <row r="8" spans="1:58" s="18" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="38" t="s">
+      <c r="B8" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="38" t="s">
+      <c r="C8" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="38" t="s">
+      <c r="D8" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="38" t="s">
+      <c r="E8" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="F8" s="38" t="s">
+      <c r="F8" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="G8" s="39" t="s">
+      <c r="G8" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="H8" s="39"/>
-      <c r="I8" s="38" t="s">
+      <c r="H8" s="36"/>
+      <c r="I8" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="J8" s="38" t="s">
+      <c r="J8" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="K8" s="38" t="s">
+      <c r="K8" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="L8" s="38" t="s">
+      <c r="L8" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="M8" s="38" t="s">
+      <c r="M8" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="N8" s="38" t="s">
+      <c r="N8" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="O8" s="38" t="s">
+      <c r="O8" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="P8" s="38" t="s">
+      <c r="P8" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="Q8" s="41"/>
-      <c r="R8" s="38" t="s">
+      <c r="Q8" s="38"/>
+      <c r="R8" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="S8" s="38"/>
-      <c r="T8" s="38" t="s">
+      <c r="S8" s="35"/>
+      <c r="T8" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="U8" s="38" t="s">
+      <c r="U8" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="V8" s="38" t="s">
+      <c r="V8" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="W8" s="40" t="s">
+      <c r="W8" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="X8" s="42" t="s">
+      <c r="X8" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="Y8" s="43" t="s">
+      <c r="Y8" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="Z8" s="40" t="s">
+      <c r="Z8" s="37" t="s">
         <v>31</v>
       </c>
-      <c r="AA8" s="40" t="s">
+      <c r="AA8" s="37" t="s">
         <v>32</v>
       </c>
-      <c r="AB8" s="40" t="s">
+      <c r="AB8" s="37" t="s">
         <v>33</v>
       </c>
-      <c r="AC8" s="40" t="s">
+      <c r="AC8" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="AD8" s="38" t="s">
+      <c r="AD8" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="AE8" s="45" t="s">
+      <c r="AE8" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="AF8" s="45"/>
+      <c r="AF8" s="42"/>
     </row>
-    <row r="9" spans="1:58" s="21" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="38"/>
-      <c r="B9" s="38"/>
-      <c r="C9" s="38"/>
-      <c r="D9" s="38"/>
-      <c r="E9" s="38"/>
-      <c r="F9" s="38"/>
-      <c r="G9" s="23" t="s">
+    <row r="9" spans="1:58" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="35"/>
+      <c r="B9" s="35"/>
+      <c r="C9" s="35"/>
+      <c r="D9" s="35"/>
+      <c r="E9" s="35"/>
+      <c r="F9" s="35"/>
+      <c r="G9" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="H9" s="23" t="s">
+      <c r="H9" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="I9" s="38"/>
-      <c r="J9" s="38"/>
-      <c r="K9" s="38"/>
-      <c r="L9" s="38"/>
-      <c r="M9" s="38"/>
-      <c r="N9" s="38"/>
-      <c r="O9" s="38"/>
-      <c r="P9" s="22" t="s">
+      <c r="I9" s="35"/>
+      <c r="J9" s="35"/>
+      <c r="K9" s="35"/>
+      <c r="L9" s="35"/>
+      <c r="M9" s="35"/>
+      <c r="N9" s="35"/>
+      <c r="O9" s="35"/>
+      <c r="P9" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="Q9" s="32" t="s">
+      <c r="Q9" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="R9" s="22" t="s">
+      <c r="R9" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="S9" s="22" t="s">
+      <c r="S9" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="T9" s="38"/>
-      <c r="U9" s="38"/>
-      <c r="V9" s="44"/>
-      <c r="W9" s="40"/>
-      <c r="X9" s="42"/>
-      <c r="Y9" s="43"/>
-      <c r="Z9" s="40"/>
-      <c r="AA9" s="40"/>
-      <c r="AB9" s="40"/>
-      <c r="AC9" s="40"/>
-      <c r="AD9" s="38"/>
-      <c r="AE9" s="22" t="s">
+      <c r="T9" s="35"/>
+      <c r="U9" s="35"/>
+      <c r="V9" s="41"/>
+      <c r="W9" s="37"/>
+      <c r="X9" s="39"/>
+      <c r="Y9" s="40"/>
+      <c r="Z9" s="37"/>
+      <c r="AA9" s="37"/>
+      <c r="AB9" s="37"/>
+      <c r="AC9" s="37"/>
+      <c r="AD9" s="35"/>
+      <c r="AE9" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="AF9" s="22" t="s">
+      <c r="AF9" s="19" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:58" x14ac:dyDescent="0.2">
-      <c r="J12" s="26" t="s">
+      <c r="J12" s="23" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2185" spans="20:20" x14ac:dyDescent="0.2">
-      <c r="T2185" s="26"/>
     </row>
   </sheetData>
-  <mergeCells count="30">
+  <mergeCells count="31">
     <mergeCell ref="AE8:AF8"/>
     <mergeCell ref="AD8:AD9"/>
     <mergeCell ref="Z8:Z9"/>
@@ -1452,21 +1427,16 @@
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="G8:H8"/>
+    <mergeCell ref="A4:M4"/>
   </mergeCells>
-  <conditionalFormatting sqref="T10:T2184">
-    <cfRule type="expression" dxfId="8" priority="8" stopIfTrue="1">
-      <formula>$AD10="-"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="9" stopIfTrue="1" operator="greaterThan">
+  <conditionalFormatting sqref="T10:T1048576">
+    <cfRule type="cellIs" dxfId="6" priority="7" stopIfTrue="1" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T2186:T1048576">
-    <cfRule type="expression" dxfId="6" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="5" priority="6" stopIfTrue="1">
       <formula>$AD2186="-"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="7" stopIfTrue="1" operator="greaterThan">
-      <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U10 U11:V1048576">
@@ -1481,7 +1451,7 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="AA10:AA1048576">
     <cfRule type="expression" dxfId="2" priority="1">
-      <formula>$AH10="DEVUELTO"</formula>
+      <formula>"ANULADO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD10:AD1048576">
